--- a/y11531/test_export_3.xlsx
+++ b/y11531/test_export_3.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887254</t>
+          <t>2026-05-26T00:45:17.368677</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887328</t>
+          <t>2026-05-26T00:45:17.368749</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887339</t>
+          <t>2026-05-26T00:45:17.368759</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887346</t>
+          <t>2026-05-26T00:45:17.368765</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887352</t>
+          <t>2026-05-26T00:45:17.368771</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887357</t>
+          <t>2026-05-26T00:45:17.368776</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887363</t>
+          <t>2026-05-26T00:45:17.368781</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887368</t>
+          <t>2026-05-26T00:45:17.368786</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.887373</t>
+          <t>2026-05-26T00:45:17.368793</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05352c4c-e8ae-4fa1-a860-2e6b337177ce</t>
+          <t>67bffa98-16ee-4080-a815-6e8c0cde0bf4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0756d18f9927ae8297b22343859994933be6adc52577d59b309bffa0ba0ee2e8_05328d4d</t>
+          <t>0756d18f9927ae8297b22343859994933be6adc52577d59b309bffa0ba0ee2e8_176e1f8e</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-26T00:01:08.886917</t>
+          <t>2026-05-26T00:45:17.368386</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[{'id': 3, 'session_id': 3, 'source_type': 'schedule', 'original_line_no': 10, 'raw_data': '{"柜员编号": NaN, "柜员姓名": "郑十一", "网点编号": "B002", "网点名称": "海淀支行", "排班日期": "2026-05-26", "班次类型": "晚班", "开始时间": "14:00", "结束时间": "20:00", "窗口号": "4", "培训标识": NaN, "请假标识": NaN, "备注": NaN}', 'error_message': '缺少必填字段: 柜员编号', 'error_type': 'VALIDATION_ERROR', 'created_at': '2026-05-26T00:01:08.887373', 'fixed': 0, 'fixed_session_id': None}]</t>
+          <t>[{'id': 3, 'session_id': 3, 'source_type': 'schedule', 'original_line_no': 10, 'raw_data': '{"柜员编号": NaN, "柜员姓名": "郑十一", "网点编号": "B002", "网点名称": "海淀支行", "排班日期": "2026-05-26", "班次类型": "晚班", "开始时间": "14:00", "结束时间": "20:00", "窗口号": "4", "培训标识": NaN, "请假标识": NaN, "备注": NaN}', 'error_message': '缺少必填字段: 柜员编号', 'error_type': 'VALIDATION_ERROR', 'created_at': '2026-05-26T00:45:17.368793', 'fixed': 0, 'fixed_session_id': None}]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'id': 17, 'session_id': 3, 'teller_id': 'T001', 'teller_name': '张三', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887254', 'is_active': 1}, {'id': 18, 'session_id': 3, 'teller_id': 'T002', 'teller_name': '李四', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887328', 'is_active': 1}, {'id': 19, 'session_id': 3, 'teller_id': 'T003', 'teller_name': '王五', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '中班', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887339', 'is_active': 1}, {'id': 20, 'session_id': 3, 'teller_id': 'T004', 'teller_name': '赵六', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '培训外出', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '4', 'is_training': 1, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887346', 'is_active': 1}, {'id': 21, 'session_id': 3, 'teller_id': 'T005', 'teller_name': '钱七', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '晚班', 'start_time': '14:00', 'end_time': '20:00', 'window_no': '5', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887352', 'is_active': 1}, {'id': 22, 'session_id': 3, 'teller_id': 'T006', 'teller_name': '孙八', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887357', 'is_active': 1}, {'id': 23, 'session_id': 3, 'teller_id': 'T007', 'teller_name': '周九', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887363', 'is_active': 1}, {'id': 24, 'session_id': 3, 'teller_id': 'T008', 'teller_name': '吴十', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '全天', 'start_time': '08:00', 'end_time': '20:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:01:08.887368', 'is_active': 1}]</t>
+          <t>[{'id': 17, 'session_id': 3, 'teller_id': 'T001', 'teller_name': '张三', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368677', 'is_active': 1}, {'id': 18, 'session_id': 3, 'teller_id': 'T002', 'teller_name': '李四', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368749', 'is_active': 1}, {'id': 19, 'session_id': 3, 'teller_id': 'T003', 'teller_name': '王五', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '中班', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368759', 'is_active': 1}, {'id': 20, 'session_id': 3, 'teller_id': 'T004', 'teller_name': '赵六', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '培训外出', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '4', 'is_training': 1, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368765', 'is_active': 1}, {'id': 21, 'session_id': 3, 'teller_id': 'T005', 'teller_name': '钱七', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '晚班', 'start_time': '14:00', 'end_time': '20:00', 'window_no': '5', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368771', 'is_active': 1}, {'id': 22, 'session_id': 3, 'teller_id': 'T006', 'teller_name': '孙八', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368776', 'is_active': 1}, {'id': 23, 'session_id': 3, 'teller_id': 'T007', 'teller_name': '周九', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368781', 'is_active': 1}, {'id': 24, 'session_id': 3, 'teller_id': 'T008', 'teller_name': '吴十', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '全天', 'start_time': '08:00', 'end_time': '20:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368786', 'is_active': 1}]</t>
         </is>
       </c>
     </row>

--- a/y11531/test_export_3.xlsx
+++ b/y11531/test_export_3.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368677</t>
+          <t>2026-05-26T01:06:55.835597</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368749</t>
+          <t>2026-05-26T01:06:55.835777</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368759</t>
+          <t>2026-05-26T01:06:55.835792</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368765</t>
+          <t>2026-05-26T01:06:55.835801</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368771</t>
+          <t>2026-05-26T01:06:55.835809</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368776</t>
+          <t>2026-05-26T01:06:55.835867</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368781</t>
+          <t>2026-05-26T01:06:55.835884</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368786</t>
+          <t>2026-05-26T01:06:55.835894</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368793</t>
+          <t>2026-05-26T01:06:55.835902</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>67bffa98-16ee-4080-a815-6e8c0cde0bf4</t>
+          <t>7a56d4f8-af48-41a5-9b9a-52b4211abbe0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0756d18f9927ae8297b22343859994933be6adc52577d59b309bffa0ba0ee2e8_176e1f8e</t>
+          <t>0756d18f9927ae8297b22343859994933be6adc52577d59b309bffa0ba0ee2e8_2daef968</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-26T00:45:17.368386</t>
+          <t>2026-05-26T01:06:55.834592</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[{'id': 3, 'session_id': 3, 'source_type': 'schedule', 'original_line_no': 10, 'raw_data': '{"柜员编号": NaN, "柜员姓名": "郑十一", "网点编号": "B002", "网点名称": "海淀支行", "排班日期": "2026-05-26", "班次类型": "晚班", "开始时间": "14:00", "结束时间": "20:00", "窗口号": "4", "培训标识": NaN, "请假标识": NaN, "备注": NaN}', 'error_message': '缺少必填字段: 柜员编号', 'error_type': 'VALIDATION_ERROR', 'created_at': '2026-05-26T00:45:17.368793', 'fixed': 0, 'fixed_session_id': None}]</t>
+          <t>[{'id': 3, 'session_id': 3, 'source_type': 'schedule', 'original_line_no': 10, 'raw_data': '{"柜员编号": NaN, "柜员姓名": "郑十一", "网点编号": "B002", "网点名称": "海淀支行", "排班日期": "2026-05-26", "班次类型": "晚班", "开始时间": "14:00", "结束时间": "20:00", "窗口号": "4", "培训标识": NaN, "请假标识": NaN, "备注": NaN}', 'error_message': '缺少必填字段: 柜员编号', 'error_type': 'VALIDATION_ERROR', 'created_at': '2026-05-26T01:06:55.835902', 'fixed': 0, 'fixed_session_id': None}]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'id': 17, 'session_id': 3, 'teller_id': 'T001', 'teller_name': '张三', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368677', 'is_active': 1}, {'id': 18, 'session_id': 3, 'teller_id': 'T002', 'teller_name': '李四', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368749', 'is_active': 1}, {'id': 19, 'session_id': 3, 'teller_id': 'T003', 'teller_name': '王五', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '中班', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368759', 'is_active': 1}, {'id': 20, 'session_id': 3, 'teller_id': 'T004', 'teller_name': '赵六', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '培训外出', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '4', 'is_training': 1, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368765', 'is_active': 1}, {'id': 21, 'session_id': 3, 'teller_id': 'T005', 'teller_name': '钱七', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '晚班', 'start_time': '14:00', 'end_time': '20:00', 'window_no': '5', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368771', 'is_active': 1}, {'id': 22, 'session_id': 3, 'teller_id': 'T006', 'teller_name': '孙八', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368776', 'is_active': 1}, {'id': 23, 'session_id': 3, 'teller_id': 'T007', 'teller_name': '周九', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368781', 'is_active': 1}, {'id': 24, 'session_id': 3, 'teller_id': 'T008', 'teller_name': '吴十', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '全天', 'start_time': '08:00', 'end_time': '20:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T00:45:17.368786', 'is_active': 1}]</t>
+          <t>[{'id': 17, 'session_id': 3, 'teller_id': 'T001', 'teller_name': '张三', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835597', 'is_active': 1}, {'id': 18, 'session_id': 3, 'teller_id': 'T002', 'teller_name': '李四', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835777', 'is_active': 1}, {'id': 19, 'session_id': 3, 'teller_id': 'T003', 'teller_name': '王五', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '中班', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835792', 'is_active': 1}, {'id': 20, 'session_id': 3, 'teller_id': 'T004', 'teller_name': '赵六', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '培训外出', 'start_time': '10:00', 'end_time': '16:00', 'window_no': '4', 'is_training': 1, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835801', 'is_active': 1}, {'id': 21, 'session_id': 3, 'teller_id': 'T005', 'teller_name': '钱七', 'branch_id': 'B001', 'branch_name': '朝阳支行', 'schedule_date': '2026-05-26', 'shift_type': '晚班', 'start_time': '14:00', 'end_time': '20:00', 'window_no': '5', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835809', 'is_active': 1}, {'id': 22, 'session_id': 3, 'teller_id': 'T006', 'teller_name': '孙八', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '1', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835867', 'is_active': 1}, {'id': 23, 'session_id': 3, 'teller_id': 'T007', 'teller_name': '周九', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '早班', 'start_time': '08:00', 'end_time': '14:00', 'window_no': '2', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835884', 'is_active': 1}, {'id': 24, 'session_id': 3, 'teller_id': 'T008', 'teller_name': '吴十', 'branch_id': 'B002', 'branch_name': '海淀支行', 'schedule_date': '2026-05-26', 'shift_type': '全天', 'start_time': '08:00', 'end_time': '20:00', 'window_no': '3', 'is_training': 0, 'is_leave': 0, 'remarks': 'nan', 'created_at': '2026-05-26T01:06:55.835894', 'is_active': 1}]</t>
         </is>
       </c>
     </row>
